--- a/plantillas_excel/20_copy_pcm_linkeo.xlsx
+++ b/plantillas_excel/20_copy_pcm_linkeo.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -640,6 +640,26 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PCM ORIGINAL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PCM COPIADO</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
         </is>
       </c>
     </row>
